--- a/diseases/d100/1995-1999.xlsx
+++ b/diseases/d100/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>11</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>6</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>8</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>3</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>6</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>7</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>3</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>3</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>4</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>3</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>4</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>3</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>7</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>4</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>4</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>3</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>12</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19859,9 +19715,6 @@
       <c r="O99" t="n">
         <v>9</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="S99" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20252,9 +20105,6 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20645,9 +20495,6 @@
       <c r="O103" t="n">
         <v>8</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21038,9 +20885,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21431,9 +21275,6 @@
       <c r="O107" t="n">
         <v>4</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21824,9 +21665,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22217,9 +22055,6 @@
       <c r="O111" t="n">
         <v>6</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22610,9 +22445,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23003,9 +22835,6 @@
       <c r="O115" t="n">
         <v>10</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23396,9 +23225,6 @@
       <c r="O117" t="n">
         <v>3</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23789,9 +23615,6 @@
       <c r="O119" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24182,9 +24005,6 @@
       <c r="O121" t="n">
         <v>4</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24575,9 +24395,6 @@
       <c r="O123" t="n">
         <v>9</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24968,9 +24785,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25361,9 +25175,6 @@
       <c r="O127" t="n">
         <v>3</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25754,9 +25565,6 @@
       <c r="O129" t="n">
         <v>3</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26147,9 +25955,6 @@
       <c r="O131" t="n">
         <v>3</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26540,9 +26345,6 @@
       <c r="O133" t="n">
         <v>3</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26933,9 +26735,6 @@
       <c r="O135" t="n">
         <v>7</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27326,9 +27125,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27719,9 +27515,6 @@
       <c r="O139" t="n">
         <v>5</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28112,9 +27905,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28505,9 +28295,6 @@
       <c r="O143" t="n">
         <v>9</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28898,9 +28685,6 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29521,9 +29305,6 @@
       <c r="O148" t="n">
         <v>5</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29914,9 +29695,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30307,9 +30085,6 @@
       <c r="O152" t="n">
         <v>7</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30700,9 +30475,6 @@
       <c r="O154" t="n">
         <v>4</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31093,9 +30865,6 @@
       <c r="O156" t="n">
         <v>7</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31486,9 +31255,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31879,9 +31645,6 @@
       <c r="O160" t="n">
         <v>6</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32272,9 +32035,6 @@
       <c r="O162" t="n">
         <v>4</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32665,9 +32425,6 @@
       <c r="O164" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33058,9 +32815,6 @@
       <c r="O166" t="n">
         <v>2</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33451,9 +33205,6 @@
       <c r="O168" t="n">
         <v>4</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33844,9 +33595,6 @@
       <c r="O170" t="n">
         <v>4</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34237,9 +33985,6 @@
       <c r="O172" t="n">
         <v>4</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34630,9 +34375,6 @@
       <c r="O174" t="n">
         <v>5</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35023,9 +34765,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35416,9 +35155,6 @@
       <c r="O178" t="n">
         <v>3</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35809,9 +35545,6 @@
       <c r="O180" t="n">
         <v>5</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36202,9 +35935,6 @@
       <c r="O182" t="n">
         <v>3</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36595,9 +36325,6 @@
       <c r="O184" t="n">
         <v>5</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36988,9 +36715,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37381,9 +37105,6 @@
       <c r="O188" t="n">
         <v>9</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37774,9 +37495,6 @@
       <c r="O190" t="n">
         <v>4</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38167,9 +37885,6 @@
       <c r="O192" t="n">
         <v>6</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38560,9 +38275,6 @@
       <c r="O194" t="n">
         <v>2</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39183,9 +38895,6 @@
       <c r="O197" t="n">
         <v>8</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39576,9 +39285,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="S199" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39969,9 +39675,6 @@
       <c r="O201" t="n">
         <v>9</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40362,9 +40065,6 @@
       <c r="O203" t="n">
         <v>1</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40755,9 +40455,6 @@
       <c r="O205" t="n">
         <v>9</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41148,9 +40845,6 @@
       <c r="O207" t="n">
         <v>4</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41541,9 +41235,6 @@
       <c r="O209" t="n">
         <v>7</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41934,9 +41625,6 @@
       <c r="O211" t="n">
         <v>2</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42327,9 +42015,6 @@
       <c r="O213" t="n">
         <v>2</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42720,9 +42405,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43113,9 +42795,6 @@
       <c r="O217" t="n">
         <v>5</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43506,9 +43185,6 @@
       <c r="O219" t="n">
         <v>3</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="S219" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43899,9 +43575,6 @@
       <c r="O221" t="n">
         <v>3</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44292,9 +43965,6 @@
       <c r="O223" t="n">
         <v>3</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44685,9 +44355,6 @@
       <c r="O225" t="n">
         <v>6</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45078,9 +44745,6 @@
       <c r="O227" t="n">
         <v>4</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45471,9 +45135,6 @@
       <c r="O229" t="n">
         <v>6</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45864,9 +45525,6 @@
       <c r="O231" t="n">
         <v>2</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46257,9 +45915,6 @@
       <c r="O233" t="n">
         <v>5</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="S233" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46650,9 +46305,6 @@
       <c r="O235" t="n">
         <v>4</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47043,9 +46695,6 @@
       <c r="O237" t="n">
         <v>4</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47436,9 +47085,6 @@
       <c r="O239" t="n">
         <v>4</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47828,9 +47474,6 @@
       </c>
       <c r="O241" t="n">
         <v>8</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>

--- a/diseases/d100/1995-1999.xlsx
+++ b/diseases/d100/1995-1999.xlsx
@@ -38616,17 +38616,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -38665,34 +38665,14 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_HIB_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_HIB_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Haemofilus influenzae sýking b</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_FR_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -38700,126 +38680,72 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications for Haemophilus influenzae type b only; this is narrower than unqualified D100 and must remain separate from all-type invasive disease. Published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>0</v>
-      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -38846,17 +38772,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -38890,25 +38816,103 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>8</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FR_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_HAEINF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Invasive Haemophilus influenzae disease</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -38927,7 +38931,7 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FR_ECDC_HAEINF_ANNUAL</t>
         </is>
       </c>
       <c r="AT197" t="n">
@@ -38940,42 +38944,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -39007,12 +39011,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -39046,29 +39050,29 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_IS_HISTORY_HIB_ANNUAL</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_IS_HISTORY_HIB_ANNUAL</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_IS_DOH_HISTORY</t>
         </is>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemofilus influenzae sýking b</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
@@ -39078,12 +39082,12 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
@@ -39093,7 +39097,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -39103,7 +39107,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -39118,7 +39122,7 @@
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="AI198" t="inlineStr">
@@ -39128,88 +39132,84 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>IS_DOH_historical_registry_annual</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Iceland historical national-registry annual notifications for Haemophilus influenzae type b only; this is narrower than unqualified D100 and must remain separate from all-type invasive disease. Published dashes mean not applicable and blank cells remain unknown.</t>
         </is>
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>no_eligible_public_projection</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -39241,12 +39241,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -39271,19 +39271,19 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -39312,12 +39312,12 @@
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT199" t="n">
@@ -39325,47 +39325,47 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -39427,38 +39427,38 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O200" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
@@ -39483,7 +39483,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -39518,17 +39518,17 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -39546,12 +39546,12 @@
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
@@ -39559,47 +39559,47 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -39631,12 +39631,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -39670,10 +39670,10 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -39682,7 +39682,7 @@
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -39702,12 +39702,12 @@
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT201" t="n">
@@ -39715,47 +39715,47 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39787,12 +39787,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -39826,29 +39826,29 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
@@ -39908,17 +39908,17 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -39936,12 +39936,12 @@
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT202" t="n">
@@ -39949,47 +39949,47 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40021,12 +40021,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -40051,19 +40051,19 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N203" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O203" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -40092,12 +40092,12 @@
       </c>
       <c r="AQ203" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT203" t="n">
@@ -40105,47 +40105,47 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40177,12 +40177,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -40207,38 +40207,38 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O204" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y204" t="inlineStr">
@@ -40263,7 +40263,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
@@ -40298,17 +40298,17 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40326,12 +40326,12 @@
       </c>
       <c r="AQ204" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT204" t="n">
@@ -40339,47 +40339,47 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40411,12 +40411,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -40450,10 +40450,10 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O205" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -40482,12 +40482,12 @@
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT205" t="n">
@@ -40495,47 +40495,47 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40567,12 +40567,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -40606,29 +40606,29 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O206" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y206" t="inlineStr">
@@ -40653,7 +40653,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -40688,17 +40688,17 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -40716,12 +40716,12 @@
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT206" t="n">
@@ -40729,47 +40729,47 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -40801,12 +40801,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -40831,19 +40831,19 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N207" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O207" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -40872,12 +40872,12 @@
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT207" t="n">
@@ -40885,47 +40885,47 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -40957,12 +40957,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -40987,38 +40987,38 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N208" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O208" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
@@ -41043,7 +41043,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -41078,17 +41078,17 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -41106,12 +41106,12 @@
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT208" t="n">
@@ -41119,47 +41119,47 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -41191,12 +41191,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -41230,10 +41230,10 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O209" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -41242,7 +41242,7 @@
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -41262,12 +41262,12 @@
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT209" t="n">
@@ -41275,47 +41275,47 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -41347,12 +41347,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -41386,29 +41386,29 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O210" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -41433,7 +41433,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -41468,17 +41468,17 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -41496,12 +41496,12 @@
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT210" t="n">
@@ -41509,47 +41509,47 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -41581,12 +41581,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -41611,19 +41611,19 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N211" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O211" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -41652,12 +41652,12 @@
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
@@ -41665,47 +41665,47 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -41737,12 +41737,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -41767,38 +41767,38 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N212" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O212" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
@@ -41823,7 +41823,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -41858,17 +41858,17 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -41886,12 +41886,12 @@
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT212" t="n">
@@ -41899,47 +41899,47 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -41971,12 +41971,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -42022,7 +42022,7 @@
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -42042,12 +42042,12 @@
       </c>
       <c r="AQ213" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT213" t="n">
@@ -42055,47 +42055,47 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42127,12 +42127,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -42173,22 +42173,22 @@
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y214" t="inlineStr">
@@ -42213,7 +42213,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -42248,17 +42248,17 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -42276,12 +42276,12 @@
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT214" t="n">
@@ -42289,47 +42289,47 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42361,12 +42361,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -42391,19 +42391,19 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -42432,12 +42432,12 @@
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT215" t="n">
@@ -42445,47 +42445,47 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42517,12 +42517,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -42547,38 +42547,38 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
@@ -42603,7 +42603,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -42638,17 +42638,17 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -42666,12 +42666,12 @@
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT216" t="n">
@@ -42679,47 +42679,47 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -42751,12 +42751,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -42790,10 +42790,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -42822,12 +42822,12 @@
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT217" t="n">
@@ -42835,47 +42835,47 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42907,12 +42907,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -42946,29 +42946,29 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
@@ -42993,7 +42993,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -43028,17 +43028,17 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -43056,12 +43056,12 @@
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT218" t="n">
@@ -43069,47 +43069,47 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43141,12 +43141,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -43171,19 +43171,19 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N219" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O219" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -43212,12 +43212,12 @@
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT219" t="n">
@@ -43225,47 +43225,47 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43297,12 +43297,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -43327,38 +43327,38 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -43383,7 +43383,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -43418,17 +43418,17 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -43446,12 +43446,12 @@
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT220" t="n">
@@ -43459,47 +43459,47 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43531,12 +43531,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -43582,7 +43582,7 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -43602,12 +43602,12 @@
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT221" t="n">
@@ -43615,47 +43615,47 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43687,12 +43687,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -43733,22 +43733,22 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -43773,7 +43773,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -43808,17 +43808,17 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -43836,12 +43836,12 @@
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -43849,47 +43849,47 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -43921,12 +43921,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -43951,12 +43951,12 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N223" t="n">
@@ -43972,7 +43972,7 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -43992,12 +43992,12 @@
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -44005,47 +44005,47 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44077,12 +44077,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -44107,12 +44107,12 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -44123,22 +44123,22 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -44163,7 +44163,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -44198,17 +44198,17 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -44226,12 +44226,12 @@
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -44239,47 +44239,47 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44311,12 +44311,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -44350,10 +44350,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O225" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -44382,12 +44382,12 @@
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -44395,47 +44395,47 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44467,12 +44467,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -44506,29 +44506,29 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O226" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -44553,7 +44553,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -44588,17 +44588,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -44616,12 +44616,12 @@
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -44629,47 +44629,47 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -44701,12 +44701,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -44731,19 +44731,19 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N227" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O227" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -44772,12 +44772,12 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT227" t="n">
@@ -44785,47 +44785,47 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44857,12 +44857,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -44887,38 +44887,38 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N228" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O228" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -44943,7 +44943,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
@@ -44978,17 +44978,17 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN228" t="b">
@@ -45006,12 +45006,12 @@
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT228" t="n">
@@ -45019,47 +45019,47 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45091,12 +45091,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -45130,10 +45130,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O229" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -45162,12 +45162,12 @@
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT229" t="n">
@@ -45175,47 +45175,47 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45247,12 +45247,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -45286,29 +45286,29 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O230" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
@@ -45333,7 +45333,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
@@ -45368,17 +45368,17 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -45396,12 +45396,12 @@
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT230" t="n">
@@ -45409,47 +45409,47 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45481,12 +45481,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -45511,19 +45511,19 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N231" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O231" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -45552,12 +45552,12 @@
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT231" t="n">
@@ -45565,47 +45565,47 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45637,12 +45637,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -45667,38 +45667,38 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N232" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O232" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X232" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y232" t="inlineStr">
@@ -45723,7 +45723,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr">
@@ -45758,17 +45758,17 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -45786,12 +45786,12 @@
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT232" t="n">
@@ -45799,47 +45799,47 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45871,12 +45871,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -45910,10 +45910,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O233" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S233" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -45942,12 +45942,12 @@
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT233" t="n">
@@ -45955,47 +45955,47 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46027,12 +46027,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -46066,29 +46066,29 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O234" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -46113,7 +46113,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -46148,17 +46148,17 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -46176,12 +46176,12 @@
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT234" t="n">
@@ -46189,47 +46189,47 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46261,12 +46261,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -46291,19 +46291,19 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -46332,12 +46332,12 @@
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT235" t="n">
@@ -46345,47 +46345,47 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46417,12 +46417,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -46447,38 +46447,38 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -46503,7 +46503,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr">
@@ -46538,17 +46538,17 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -46566,12 +46566,12 @@
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT236" t="n">
@@ -46579,47 +46579,47 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46651,12 +46651,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -46702,7 +46702,7 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -46722,12 +46722,12 @@
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT237" t="n">
@@ -46735,47 +46735,47 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -46807,12 +46807,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -46853,22 +46853,22 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -46928,17 +46928,17 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -46956,12 +46956,12 @@
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT238" t="n">
@@ -46969,47 +46969,47 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47041,12 +47041,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -47071,12 +47071,12 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-11-01</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="N239" t="n">
@@ -47092,7 +47092,7 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -47112,12 +47112,12 @@
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT239" t="n">
@@ -47125,47 +47125,47 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -47197,12 +47197,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -47227,12 +47227,12 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-11-01</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="N240" t="n">
@@ -47243,22 +47243,22 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X240" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae,total</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y240" t="inlineStr">
@@ -47283,7 +47283,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
@@ -47318,17 +47318,17 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -47346,12 +47346,12 @@
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT240" t="n">
@@ -47359,47 +47359,47 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -47431,12 +47431,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -47470,10 +47470,10 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O241" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -47502,12 +47502,12 @@
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT241" t="n">
@@ -47515,47 +47515,47 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -47587,12 +47587,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -47626,29 +47626,29 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O242" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X242" t="inlineStr">
         <is>
-          <t>Syst. H. influenzae-sykdom</t>
+          <t>Haemophilus influenzae,total</t>
         </is>
       </c>
       <c r="Y242" t="inlineStr">
@@ -47673,7 +47673,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -47708,17 +47708,17 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -47736,12 +47736,12 @@
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -47749,45 +47749,435 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA242" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>8</v>
+      </c>
+      <c r="O243" t="n">
+        <v>8</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV242" t="inlineStr">
+      <c r="AV243" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW242" t="inlineStr">
+      <c r="AW243" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX242" t="inlineStr">
+      <c r="AX243" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY242" t="inlineStr">
+      <c r="AY243" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ242" t="inlineStr">
+      <c r="AZ243" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA242" t="inlineStr">
+      <c r="BA243" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB242" t="inlineStr">
+      <c r="BB243" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC242" t="inlineStr">
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>8</v>
+      </c>
+      <c r="O244" t="n">
+        <v>8</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN244" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -47909,7 +48299,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -47919,7 +48309,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -47939,7 +48329,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -47949,7 +48339,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
